--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/MAINE_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/MAINE_2012.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C11">
